--- a/data/trans_orig/Q5410A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5410A_2023-Provincia-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W58"/>
+  <dimension ref="A1:W52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si necesita  enema o supositorio y es capaz de utilizarlos en 2023</t>
+          <t>Población según si necesita  enema o supositorio y es capaz de utilizarlos en 2023 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -710,7 +710,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -755,72 +755,72 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>594</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,22%</t>
         </is>
       </c>
     </row>
@@ -833,12 +833,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>865</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -868,72 +868,72 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,94%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1094,72 +1094,72 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>596</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>596</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1207,72 +1207,72 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,07%</t>
         </is>
       </c>
     </row>
@@ -1285,114 +1285,114 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>865</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>865</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>865</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>633</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,92 +1417,92 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>45,85%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2243</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4744</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>74,32%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>395</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>84,01%</t>
         </is>
       </c>
     </row>
@@ -1520,102 +1520,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>567</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>30,9%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>571</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>73,46%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,82 +1766,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1854,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>636</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,67 +1869,67 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1623</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>25,69%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>80,91%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1011</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2936</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>15,83%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>45,99%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -1967,22 +1967,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2002,22 +2002,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2084,47 +2084,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1835</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>34,47%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>436</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,42 +2149,42 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>436</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>58,43%</t>
         </is>
       </c>
     </row>
@@ -2202,102 +2202,102 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>754</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>380</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>483</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>88,55%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,22 +2448,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>413</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,32 +2473,32 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>413</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,22 +2508,22 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -2536,82 +2536,82 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1835</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>34,64%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1767</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>18,06%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>69,18%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>25,69%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>79,77%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>461</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>59,9%</t>
         </is>
       </c>
     </row>
@@ -2649,22 +2649,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>754</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>754</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>754</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,22 +2684,22 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,82 +2791,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2884,102 +2884,102 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>476</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>80,72%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3105,12 +3105,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>503</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3120,32 +3120,32 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>788</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3170,42 +3170,42 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>376</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -3218,12 +3218,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>924</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,92 +3233,92 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>351</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>791</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>46,86%</t>
         </is>
       </c>
     </row>
@@ -3331,22 +3331,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3366,22 +3366,22 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3401,22 +3401,22 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Huelva</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3448,107 +3448,107 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>519</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3591,77 +3591,77 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>328</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>847</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,22 +3699,22 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>395</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3724,32 +3724,32 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>395</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3759,22 +3759,22 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -3787,47 +3787,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1460</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>26,44%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>76,73%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>611</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3837,57 +3837,57 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
+          <t>2423</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>15,92%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>63,15%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
           <t>2785</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>11,51%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>40,68%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>1292</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>3190</t>
-        </is>
-      </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>947</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>2369</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3930,77 +3930,77 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>947</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>45,03%</t>
         </is>
       </c>
     </row>
@@ -4013,22 +4013,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4048,22 +4048,22 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4083,22 +4083,22 @@
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Jaén</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4130,107 +4130,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>390</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>538</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>50,68%</t>
         </is>
       </c>
     </row>
@@ -4243,12 +4243,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4273,77 +4273,77 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>536</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>70,57%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,82 +4494,82 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4582,47 +4582,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>32,45%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>2325</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>30,17%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>74,06%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -4632,57 +4632,57 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>511</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>51,43%</t>
         </is>
       </c>
     </row>
@@ -4695,22 +4695,22 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4765,22 +4765,22 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>8516</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>8516</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>8516</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,82 +4837,82 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4955,77 +4955,77 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3934</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>8,9%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>26,75%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>2288</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>4322</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>36,8%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>69,53%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>536</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>536</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -5151,107 +5151,107 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>10898</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>71,36%</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>615</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5294,77 +5294,77 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>48,42%</t>
         </is>
       </c>
     </row>
@@ -5377,22 +5377,22 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5412,22 +5412,22 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5447,22 +5447,22 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -5494,107 +5494,107 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10198</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>14510</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -5607,107 +5607,107 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>13161</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>37</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>19119</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>14287</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>24673</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,82 +5745,82 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>406</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>399</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -5833,107 +5833,107 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>10721</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>12762</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>8275</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>13186</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -5946,107 +5946,107 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>13333</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>8815</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>17920</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -6059,22 +6059,22 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>14483</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>14483</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>14483</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6094,22 +6094,22 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>42551</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>42551</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>42551</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6129,22 +6129,22 @@
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>108</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>57033</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>57033</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>57033</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6164,700 +6164,17 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>No soy capaz de usarlo</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>2306</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>817</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>4851</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>15,92%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>33,5%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>7893</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>4821</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>12509</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>18,55%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>11,33%</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>29,4%</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>10198</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>6687</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>14871</t>
-        </is>
-      </c>
-      <c r="U52" s="2" t="inlineStr">
-        <is>
-          <t>17,88%</t>
-        </is>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="W52" s="2" t="inlineStr">
-        <is>
-          <t>26,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n"/>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>No utilizo enema o supositorio</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>5958</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>2835</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>8834</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>41,14%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>19,58%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>61,0%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>13161</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>9308</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>17996</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>30,93%</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>21,88%</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>42,29%</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>19119</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>14045</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>24380</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>33,52%</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>24,63%</t>
-        </is>
-      </c>
-      <c r="W53" s="2" t="inlineStr">
-        <is>
-          <t>42,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n"/>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>Sí, por otro</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>6205</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>14,58%</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="inlineStr">
-        <is>
-          <t>6109</t>
-        </is>
-      </c>
-      <c r="U54" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="W54" s="2" t="inlineStr">
-        <is>
-          <t>10,71%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n"/>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>Sí, con ayuda</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>2351</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>5016</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>16,23%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>34,64%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>10411</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>6507</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>15254</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>24,47%</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>15,29%</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>35,85%</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>12762</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="inlineStr">
-        <is>
-          <t>8438</t>
-        </is>
-      </c>
-      <c r="T55" s="2" t="inlineStr">
-        <is>
-          <t>18274</t>
-        </is>
-      </c>
-      <c r="U55" s="2" t="inlineStr">
-        <is>
-          <t>22,38%</t>
-        </is>
-      </c>
-      <c r="V55" s="2" t="inlineStr">
-        <is>
-          <t>14,79%</t>
-        </is>
-      </c>
-      <c r="W55" s="2" t="inlineStr">
-        <is>
-          <t>32,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n"/>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>Sí, por sí solo/a</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>3868</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>1533</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>6811</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>26,71%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>10,59%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>47,03%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>9123</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>5855</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>13029</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>21,44%</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>13,76%</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>30,62%</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>12991</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>8833</t>
-        </is>
-      </c>
-      <c r="T56" s="2" t="inlineStr">
-        <is>
-          <t>17671</t>
-        </is>
-      </c>
-      <c r="U56" s="2" t="inlineStr">
-        <is>
-          <t>22,78%</t>
-        </is>
-      </c>
-      <c r="V56" s="2" t="inlineStr">
-        <is>
-          <t>15,49%</t>
-        </is>
-      </c>
-      <c r="W56" s="2" t="inlineStr">
-        <is>
-          <t>30,98%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="n"/>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>14483</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>14483</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>14483</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>42551</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>42551</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>42551</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="R57" s="2" t="inlineStr">
-        <is>
-          <t>57033</t>
-        </is>
-      </c>
-      <c r="S57" s="2" t="inlineStr">
-        <is>
-          <t>57033</t>
-        </is>
-      </c>
-      <c r="T57" s="2" t="inlineStr">
-        <is>
-          <t>57033</t>
-        </is>
-      </c>
-      <c r="U57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A40:A45"/>
-    <mergeCell ref="A52:A57"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A46:A51"/>
     <mergeCell ref="A16:A21"/>

--- a/data/trans_orig/Q5410A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5410A_2023-Provincia-trans_orig.xlsx
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2374</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2374</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>67,24%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>643</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>643</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>38,07%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>926</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>921</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,33%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>533</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>573</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>69,55%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>609</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>533</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,42%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>452</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>452</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,56%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>844</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>377</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>431</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>431</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>487</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>487</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,63%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>844</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>844</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>844</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>518</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,38%</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>492</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>815</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>380</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>970</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>383</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>852</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>49,07%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>458</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>506</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>358</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>864</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>40,22%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>405</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>406</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>650</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>650</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>931</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2369</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>931</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>76,05%</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>52,15%</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>891</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>54,14%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4975,12 +4975,12 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>720</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>592</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>592</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10898</t>
+          <t>13332</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>13124</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>72,44%</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>663</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7779</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>8906</t>
+          <t>9823</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>17657</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>17657</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>17657</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>21703</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>21703</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>21703</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>790</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>10198</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>19335</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>20662</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>24673</t>
+          <t>27657</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>409</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>412</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>15272</t>
+          <t>18232</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>14968</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>14228</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>62729</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>62729</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>62729</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
